--- a/OnTheSnow_v1.xlsx
+++ b/OnTheSnow_v1.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoursesUSU\Final_Semester\Intro_Reg_ML\Project 1\archive (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoursesUSU\Final_Semester\Intro_Reg_ML\DATA5600\data-5600\Project1\Data-5600-Project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EDBE55-83C2-41E2-8810-A93A4FD0E52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21026320-2119-4367-963E-700C2BCE5A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="743">
   <si>
     <t>Name</t>
   </si>
@@ -2246,6 +2259,9 @@
   </si>
   <si>
     <t>Check year open info</t>
+  </si>
+  <si>
+    <t>sentiment</t>
   </si>
 </sst>
 </file>
@@ -2291,7 +2307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2314,17 +2330,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2631,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK331"/>
+  <dimension ref="A1:AL331"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" bestFit="1" customWidth="1"/>
@@ -2648,7 +2678,7 @@
     <col min="28" max="28" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2760,8 +2790,11 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL1" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2846,8 +2879,12 @@
       <c r="AE2">
         <v>550</v>
       </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL2">
+        <f ca="1">RANDBETWEEN(1,7)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -2929,8 +2966,12 @@
       <c r="AB3">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL3">
+        <f t="shared" ref="AL3:AL66" ca="1" si="0">RANDBETWEEN(1,7)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -3015,8 +3056,12 @@
       <c r="AE4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL4">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -3098,8 +3143,12 @@
       <c r="AB5">
         <v>122</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL5">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -3184,8 +3233,12 @@
       <c r="AF6" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL6">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -3264,8 +3317,12 @@
       <c r="AB7">
         <v>107</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL7">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -3347,8 +3404,12 @@
       <c r="AD8" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL8">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -3430,8 +3491,12 @@
       <c r="AD9" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL9">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -3516,8 +3581,12 @@
       <c r="AE10">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL10">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3596,8 +3665,12 @@
       <c r="AB11">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL11">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -3679,8 +3752,12 @@
       <c r="AB12">
         <v>170</v>
       </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL12">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3839,12 @@
       <c r="AD13" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL13">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -3842,8 +3923,12 @@
       <c r="AF14" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL14">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -3925,8 +4010,12 @@
       <c r="AD15" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL15">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -4008,8 +4097,12 @@
       <c r="AA16" s="2" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -4091,8 +4184,12 @@
       <c r="AF17" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL17">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -4177,8 +4274,12 @@
       <c r="AF18" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL18">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -4257,8 +4358,12 @@
       <c r="AF19" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL19">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -4340,8 +4445,12 @@
       <c r="AD20" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL20">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -4423,8 +4532,12 @@
       <c r="AF21" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL21">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -4509,8 +4622,12 @@
       <c r="AH22">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL22">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -4595,8 +4712,12 @@
       <c r="AE23">
         <v>150</v>
       </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL23">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -4681,8 +4802,12 @@
       <c r="AF24" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL24">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -4761,8 +4886,12 @@
       <c r="AF25" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL25">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -4844,8 +4973,12 @@
       <c r="AB26">
         <v>150</v>
       </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL26">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -4924,8 +5057,12 @@
       <c r="AB27">
         <v>144</v>
       </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL27">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -5007,8 +5144,12 @@
       <c r="AB28">
         <v>233</v>
       </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL28">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -5090,8 +5231,12 @@
       <c r="AB29">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL29">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -5173,8 +5318,12 @@
       <c r="AD30" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL30">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -5256,8 +5405,12 @@
       <c r="AD31" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL31">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -5339,8 +5492,12 @@
       <c r="AB32">
         <v>164</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL32">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -5422,8 +5579,12 @@
       <c r="AD33" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL33">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -5505,8 +5666,12 @@
       <c r="AB34">
         <v>130</v>
       </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL34">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -5588,8 +5753,12 @@
       <c r="AD35" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL35">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -5674,8 +5843,12 @@
       <c r="AF36" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL36">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -5760,8 +5933,12 @@
       <c r="AE37">
         <v>288</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL37">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -5843,8 +6020,12 @@
       <c r="AB38">
         <v>184</v>
       </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL38">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -5923,8 +6104,12 @@
       <c r="AB39">
         <v>136</v>
       </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL39">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -6006,8 +6191,12 @@
       <c r="AB40">
         <v>110</v>
       </c>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL40">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -6083,8 +6272,12 @@
       <c r="AG41">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL41">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -6163,8 +6356,12 @@
       <c r="AB42">
         <v>130</v>
       </c>
-    </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL42">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -6249,8 +6446,12 @@
       <c r="AE43">
         <v>100</v>
       </c>
-    </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL43">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -6335,8 +6536,12 @@
       <c r="AE44">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL44">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -6418,8 +6623,12 @@
       <c r="AB45">
         <v>135</v>
       </c>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL45">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>81</v>
       </c>
@@ -6501,8 +6710,12 @@
       <c r="AB46">
         <v>137</v>
       </c>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL46">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -6584,8 +6797,12 @@
       <c r="AD47" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL47">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>83</v>
       </c>
@@ -6667,8 +6884,12 @@
       <c r="AD48" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL48">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -6747,8 +6968,12 @@
       <c r="AB49">
         <v>150</v>
       </c>
-    </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL49">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -6830,8 +7055,12 @@
       <c r="AF50" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL50">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -6916,8 +7145,12 @@
       <c r="AF51" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL51">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -7002,8 +7235,12 @@
       <c r="AE52">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL52">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -7088,8 +7325,12 @@
       <c r="AE53">
         <v>66</v>
       </c>
-    </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL53">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -7174,8 +7415,12 @@
       <c r="AF54" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL54">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -7257,8 +7502,12 @@
       <c r="AF55" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL55">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -7340,8 +7589,12 @@
       <c r="AF56" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL56">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -7417,8 +7670,12 @@
       <c r="AF57" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL57">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -7497,8 +7754,12 @@
       <c r="AB58">
         <v>140</v>
       </c>
-    </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL58">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -7574,8 +7835,12 @@
       <c r="AF59" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL59">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -7663,8 +7928,12 @@
       <c r="AG60">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL60">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -7749,8 +8018,12 @@
       <c r="AF61" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL61">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -7835,8 +8108,12 @@
       <c r="AE62">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL62">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -7921,8 +8198,12 @@
       <c r="AE63">
         <v>20</v>
       </c>
-    </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL63">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -7998,8 +8279,12 @@
       <c r="AJ64" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL64">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -8081,8 +8366,12 @@
       <c r="AD65" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL65">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -8164,8 +8453,12 @@
       <c r="AB66">
         <v>150</v>
       </c>
-    </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL66">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>102</v>
       </c>
@@ -8250,8 +8543,12 @@
       <c r="AF67" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL67">
+        <f t="shared" ref="AL67:AL130" ca="1" si="1">RANDBETWEEN(1,7)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>103</v>
       </c>
@@ -8336,8 +8633,12 @@
       <c r="AF68" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL68">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>104</v>
       </c>
@@ -8422,8 +8723,12 @@
       <c r="AF69" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL69">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>105</v>
       </c>
@@ -8508,8 +8813,12 @@
       <c r="AF70" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL70">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -8594,8 +8903,12 @@
       <c r="AE71">
         <v>65</v>
       </c>
-    </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL71">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>107</v>
       </c>
@@ -8680,8 +8993,12 @@
       <c r="AF72" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL72">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>108</v>
       </c>
@@ -8763,8 +9080,12 @@
       <c r="AF73" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL73">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -8849,8 +9170,12 @@
       <c r="AE74">
         <v>35</v>
       </c>
-    </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL74">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -8932,8 +9257,12 @@
       <c r="AF75" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL75">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -9006,8 +9335,12 @@
       <c r="AJ76" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL76">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -9092,8 +9425,12 @@
       <c r="AF77" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL77">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -9178,8 +9515,12 @@
       <c r="AF78" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL78">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -9261,8 +9602,12 @@
       <c r="AB79">
         <v>120</v>
       </c>
-    </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL79">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>115</v>
       </c>
@@ -9335,8 +9680,12 @@
       <c r="AJ80" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL80">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>116</v>
       </c>
@@ -9418,8 +9767,12 @@
       <c r="AF81" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL81">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>117</v>
       </c>
@@ -9504,8 +9857,12 @@
       <c r="AF82" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL82">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -9587,8 +9944,12 @@
       <c r="AB83">
         <v>155</v>
       </c>
-    </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL83">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>119</v>
       </c>
@@ -9673,8 +10034,12 @@
       <c r="AE84">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL84">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -9759,8 +10124,12 @@
       <c r="AF85" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL85">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -9845,8 +10214,12 @@
       <c r="AF86" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL86">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -9928,8 +10301,12 @@
       <c r="AE87">
         <v>70</v>
       </c>
-    </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL87">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -10005,8 +10382,12 @@
       <c r="AJ88" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL88">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -10088,8 +10469,12 @@
       <c r="AF89" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL89">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -10168,8 +10553,12 @@
       <c r="AJ90" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL90">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -10254,8 +10643,12 @@
       <c r="AE91">
         <v>104</v>
       </c>
-    </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL91">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>127</v>
       </c>
@@ -10340,8 +10733,12 @@
       <c r="AF92" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL92">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -10426,8 +10823,12 @@
       <c r="AF93" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL93">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -10512,8 +10913,12 @@
       <c r="AH94">
         <v>14</v>
       </c>
-    </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL94">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>130</v>
       </c>
@@ -10598,8 +11003,12 @@
       <c r="AE95">
         <v>38</v>
       </c>
-    </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL95">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -10687,8 +11096,12 @@
       <c r="AG96">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL96">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>132</v>
       </c>
@@ -10770,8 +11183,12 @@
       <c r="AF97" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL97">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -10847,8 +11264,12 @@
       <c r="AE98">
         <v>80</v>
       </c>
-    </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL98">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>134</v>
       </c>
@@ -10930,8 +11351,12 @@
       <c r="AB99">
         <v>108</v>
       </c>
-    </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL99">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -11016,8 +11441,12 @@
       <c r="AE100">
         <v>100</v>
       </c>
-    </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL100">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -11099,8 +11528,12 @@
       <c r="AB101">
         <v>115</v>
       </c>
-    </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL101">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -11185,8 +11618,12 @@
       <c r="AF102" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL102">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -11271,8 +11708,12 @@
       <c r="AF103" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL103">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -11357,8 +11798,12 @@
       <c r="AF104" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -11437,8 +11882,12 @@
       <c r="AF105" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL105">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -11526,8 +11975,12 @@
       <c r="AG106">
         <v>56.5</v>
       </c>
-    </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL106">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -11609,8 +12062,12 @@
       <c r="AF107" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL107">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>143</v>
       </c>
@@ -11695,8 +12152,12 @@
       <c r="AF108" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL108">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>144</v>
       </c>
@@ -11781,8 +12242,12 @@
       <c r="AF109" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL109">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>145</v>
       </c>
@@ -11855,8 +12320,12 @@
       <c r="AF110" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL110">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>146</v>
       </c>
@@ -11941,8 +12410,12 @@
       <c r="AF111" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AL111">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -12024,8 +12497,12 @@
       <c r="AF112" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="113" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL112">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -12107,8 +12584,12 @@
       <c r="AE113">
         <v>100</v>
       </c>
-    </row>
-    <row r="114" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL113">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>149</v>
       </c>
@@ -12187,8 +12668,12 @@
       <c r="AF114" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="115" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL114">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -12273,8 +12758,12 @@
       <c r="AF115" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="116" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL115">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>151</v>
       </c>
@@ -12359,8 +12848,12 @@
       <c r="AF116" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="117" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL116">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>152</v>
       </c>
@@ -12439,8 +12932,12 @@
       <c r="AJ117" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL117">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -12525,8 +13022,12 @@
       <c r="AE118">
         <v>80</v>
       </c>
-    </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL118">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>154</v>
       </c>
@@ -12611,8 +13112,12 @@
       <c r="AE119">
         <v>70</v>
       </c>
-    </row>
-    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL119">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>155</v>
       </c>
@@ -12697,8 +13202,12 @@
       <c r="AE120">
         <v>40</v>
       </c>
-    </row>
-    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL120">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -12780,8 +13289,12 @@
       <c r="AJ121" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL121">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -12866,8 +13379,12 @@
       <c r="AF122" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL122">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -12952,8 +13469,12 @@
       <c r="AF123" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL123">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -13038,8 +13559,12 @@
       <c r="AJ124" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL124">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -13124,8 +13649,12 @@
       <c r="AF125" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL125">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -13210,8 +13739,12 @@
       <c r="AE126">
         <v>250</v>
       </c>
-    </row>
-    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL126">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -13296,8 +13829,12 @@
       <c r="AE127">
         <v>35</v>
       </c>
-    </row>
-    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL127">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -13379,8 +13916,12 @@
       <c r="AF128" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL128">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -13462,8 +14003,12 @@
       <c r="AF129" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL129">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>165</v>
       </c>
@@ -13548,8 +14093,12 @@
       <c r="AE130">
         <v>35</v>
       </c>
-    </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL130">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>166</v>
       </c>
@@ -13631,8 +14180,12 @@
       <c r="AF131" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL131">
+        <f t="shared" ref="AL131:AL194" ca="1" si="2">RANDBETWEEN(1,7)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>167</v>
       </c>
@@ -13717,8 +14270,12 @@
       <c r="AF132" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL132">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>168</v>
       </c>
@@ -13803,8 +14360,12 @@
       <c r="AE133">
         <v>35</v>
       </c>
-    </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL133">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>169</v>
       </c>
@@ -13886,8 +14447,12 @@
       <c r="AB134">
         <v>127</v>
       </c>
-    </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL134">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>170</v>
       </c>
@@ -13972,8 +14537,12 @@
       <c r="AF135" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL135">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>171</v>
       </c>
@@ -14055,8 +14624,12 @@
       <c r="AF136" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL136">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>172</v>
       </c>
@@ -14141,8 +14714,12 @@
       <c r="AF137" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL137">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>173</v>
       </c>
@@ -14227,8 +14804,12 @@
       <c r="AF138" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL138">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>174</v>
       </c>
@@ -14313,8 +14894,12 @@
       <c r="AE139">
         <v>100</v>
       </c>
-    </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL139">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>175</v>
       </c>
@@ -14393,8 +14978,12 @@
       <c r="AE140">
         <v>17</v>
       </c>
-    </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL140">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>176</v>
       </c>
@@ -14488,8 +15077,12 @@
       <c r="AI141">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL141">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>177</v>
       </c>
@@ -14571,8 +15164,12 @@
       <c r="AD142" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL142">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>178</v>
       </c>
@@ -14645,8 +15242,12 @@
       <c r="AF143" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL143">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -14728,8 +15329,12 @@
       <c r="AB144">
         <v>133</v>
       </c>
-    </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL144">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>180</v>
       </c>
@@ -14811,8 +15416,12 @@
       <c r="AB145">
         <v>116</v>
       </c>
-    </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL145">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -14903,8 +15512,12 @@
       <c r="AI146">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL146">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>182</v>
       </c>
@@ -14983,8 +15596,12 @@
       <c r="AF147" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL147">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>183</v>
       </c>
@@ -15057,8 +15674,12 @@
       <c r="AF148" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL148">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>184</v>
       </c>
@@ -15137,8 +15758,12 @@
       <c r="AF149" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL149">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>185</v>
       </c>
@@ -15220,8 +15845,12 @@
       <c r="AB150">
         <v>136</v>
       </c>
-    </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL150">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>186</v>
       </c>
@@ -15300,8 +15929,12 @@
       <c r="AB151">
         <v>85</v>
       </c>
-    </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL151">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>187</v>
       </c>
@@ -15380,8 +16013,12 @@
       <c r="AF152" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL152">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>188</v>
       </c>
@@ -15466,8 +16103,12 @@
       <c r="AE153">
         <v>600</v>
       </c>
-    </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL153">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>189</v>
       </c>
@@ -15549,8 +16190,12 @@
       <c r="AF154" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL154">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -15629,8 +16274,12 @@
       <c r="AF155" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL155">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>191</v>
       </c>
@@ -15712,8 +16361,12 @@
       <c r="AF156" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL156">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>192</v>
       </c>
@@ -15795,8 +16448,12 @@
       <c r="AB157">
         <v>150</v>
       </c>
-    </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL157">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>193</v>
       </c>
@@ -15878,8 +16535,12 @@
       <c r="AF158" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL158">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>194</v>
       </c>
@@ -15958,8 +16619,12 @@
       <c r="AB159">
         <v>107</v>
       </c>
-    </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL159">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>195</v>
       </c>
@@ -16044,8 +16709,12 @@
       <c r="AE160">
         <v>45</v>
       </c>
-    </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL160">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>196</v>
       </c>
@@ -16127,8 +16796,12 @@
       <c r="AB161">
         <v>143</v>
       </c>
-    </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL161">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>197</v>
       </c>
@@ -16210,8 +16883,12 @@
       <c r="AD162" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL162">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>198</v>
       </c>
@@ -16296,8 +16973,12 @@
       <c r="AE163">
         <v>100</v>
       </c>
-    </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL163">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>199</v>
       </c>
@@ -16379,8 +17060,12 @@
       <c r="AB164">
         <v>105</v>
       </c>
-    </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL164">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>200</v>
       </c>
@@ -16465,8 +17150,12 @@
       <c r="AF165" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL165">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>201</v>
       </c>
@@ -16551,8 +17240,12 @@
       <c r="AF166" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL166">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -16634,8 +17327,12 @@
       <c r="AF167" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL167">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -16717,8 +17414,12 @@
       <c r="AF168" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL168">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>204</v>
       </c>
@@ -16803,8 +17504,12 @@
       <c r="AF169" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL169">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>205</v>
       </c>
@@ -16886,8 +17591,12 @@
       <c r="AF170" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL170">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>206</v>
       </c>
@@ -16969,8 +17678,12 @@
       <c r="AF171" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL171">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>207</v>
       </c>
@@ -17055,8 +17768,12 @@
       <c r="AF172" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL172">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>208</v>
       </c>
@@ -17135,8 +17852,12 @@
       <c r="AF173" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL173">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>209</v>
       </c>
@@ -17221,8 +17942,12 @@
       <c r="AF174" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL174">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>210</v>
       </c>
@@ -17307,8 +18032,12 @@
       <c r="AF175" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="AL175">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>211</v>
       </c>
@@ -17393,8 +18122,12 @@
       <c r="AE176">
         <v>50</v>
       </c>
-    </row>
-    <row r="177" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL176">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>212</v>
       </c>
@@ -17470,8 +18203,12 @@
       <c r="AF177" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="178" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL177">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>213</v>
       </c>
@@ -17553,8 +18290,12 @@
       <c r="AF178" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="179" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL178">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>214</v>
       </c>
@@ -17633,8 +18374,12 @@
       <c r="AA179" s="2" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="180" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL179">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>215</v>
       </c>
@@ -17716,8 +18461,12 @@
       <c r="AF180" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="181" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL180">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>216</v>
       </c>
@@ -17799,8 +18548,12 @@
       <c r="AF181" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="182" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL181">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>217</v>
       </c>
@@ -17882,8 +18635,12 @@
       <c r="AF182" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="183" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL182">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>218</v>
       </c>
@@ -17965,8 +18722,12 @@
       <c r="AB183">
         <v>130</v>
       </c>
-    </row>
-    <row r="184" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL183">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>219</v>
       </c>
@@ -18051,8 +18812,12 @@
       <c r="AH184">
         <v>13</v>
       </c>
-    </row>
-    <row r="185" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL184">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>220</v>
       </c>
@@ -18134,8 +18899,12 @@
       <c r="AB185">
         <v>150</v>
       </c>
-    </row>
-    <row r="186" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL185">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>221</v>
       </c>
@@ -18211,8 +18980,12 @@
       <c r="AF186" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="187" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL186">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>222</v>
       </c>
@@ -18297,8 +19070,12 @@
       <c r="AE187">
         <v>154</v>
       </c>
-    </row>
-    <row r="188" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL187">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>223</v>
       </c>
@@ -18377,8 +19154,12 @@
       <c r="AJ188" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="189" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL188">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>224</v>
       </c>
@@ -18469,8 +19250,12 @@
       <c r="AI189">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="190" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL189">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>225</v>
       </c>
@@ -18552,8 +19337,12 @@
       <c r="AF190" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="191" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL190">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>226</v>
       </c>
@@ -18647,8 +19436,12 @@
       <c r="AI191">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="192" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL191">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>227</v>
       </c>
@@ -18733,8 +19526,12 @@
       <c r="AE192">
         <v>175</v>
       </c>
-    </row>
-    <row r="193" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL192">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>228</v>
       </c>
@@ -18816,8 +19613,12 @@
       <c r="AE193">
         <v>37</v>
       </c>
-    </row>
-    <row r="194" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL193">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>229</v>
       </c>
@@ -18902,8 +19703,12 @@
       <c r="AF194" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="195" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL194">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>230</v>
       </c>
@@ -18985,8 +19790,12 @@
       <c r="AF195" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="196" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL195">
+        <f t="shared" ref="AL195:AL258" ca="1" si="3">RANDBETWEEN(1,7)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>231</v>
       </c>
@@ -19071,8 +19880,12 @@
       <c r="AE196">
         <v>400</v>
       </c>
-    </row>
-    <row r="197" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL196">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>232</v>
       </c>
@@ -19154,8 +19967,12 @@
       <c r="AF197" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="198" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL197">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>233</v>
       </c>
@@ -19240,8 +20057,12 @@
       <c r="AF198" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="199" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL198">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>234</v>
       </c>
@@ -19326,8 +20147,12 @@
       <c r="AF199" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="200" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL199">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>235</v>
       </c>
@@ -19406,8 +20231,12 @@
       <c r="AJ200" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="201" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL200">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>236</v>
       </c>
@@ -19489,8 +20318,12 @@
       <c r="AB201">
         <v>105</v>
       </c>
-    </row>
-    <row r="202" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL201">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>237</v>
       </c>
@@ -19575,8 +20408,12 @@
       <c r="AF202" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="203" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL202">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>238</v>
       </c>
@@ -19658,8 +20495,12 @@
       <c r="AE203">
         <v>12</v>
       </c>
-    </row>
-    <row r="204" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL203">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>239</v>
       </c>
@@ -19744,8 +20585,12 @@
       <c r="AF204" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="205" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL204">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>240</v>
       </c>
@@ -19830,8 +20675,12 @@
       <c r="AG205">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="206" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL205">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>241</v>
       </c>
@@ -19907,8 +20756,12 @@
       <c r="AF206" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="207" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL206">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>242</v>
       </c>
@@ -19993,8 +20846,12 @@
       <c r="AF207" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="208" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL207">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>243</v>
       </c>
@@ -20076,8 +20933,12 @@
       <c r="AF208" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="209" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL208">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>244</v>
       </c>
@@ -20162,8 +21023,12 @@
       <c r="AF209" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="210" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL209">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>245</v>
       </c>
@@ -20245,8 +21110,12 @@
       <c r="AJ210" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="211" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL210">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>246</v>
       </c>
@@ -20337,8 +21206,12 @@
       <c r="AI211">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="212" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL211">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>247</v>
       </c>
@@ -20420,8 +21293,12 @@
       <c r="AF212" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="213" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL212">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>248</v>
       </c>
@@ -20506,8 +21383,12 @@
       <c r="AF213" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="214" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL213">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>249</v>
       </c>
@@ -20589,8 +21470,12 @@
       <c r="AB214">
         <v>141</v>
       </c>
-    </row>
-    <row r="215" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL214">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>250</v>
       </c>
@@ -20672,8 +21557,12 @@
       <c r="AF215" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="216" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL215">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>251</v>
       </c>
@@ -20761,8 +21650,12 @@
       <c r="AG216">
         <v>12</v>
       </c>
-    </row>
-    <row r="217" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL216">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>252</v>
       </c>
@@ -20841,8 +21734,12 @@
       <c r="AF217" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="218" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL217">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>253</v>
       </c>
@@ -20927,8 +21824,12 @@
       <c r="AE218">
         <v>27</v>
       </c>
-    </row>
-    <row r="219" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL218">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>254</v>
       </c>
@@ -21019,8 +21920,12 @@
       <c r="AI219">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="220" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL219">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>255</v>
       </c>
@@ -21105,8 +22010,12 @@
       <c r="AG220">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="221" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL220">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>256</v>
       </c>
@@ -21191,8 +22100,12 @@
       <c r="AE221">
         <v>95</v>
       </c>
-    </row>
-    <row r="222" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL221">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>257</v>
       </c>
@@ -21277,8 +22190,12 @@
       <c r="AE222">
         <v>95</v>
       </c>
-    </row>
-    <row r="223" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL222">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>258</v>
       </c>
@@ -21363,8 +22280,12 @@
       <c r="AF223" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="224" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL223">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>259</v>
       </c>
@@ -21449,8 +22370,12 @@
       <c r="AE224">
         <v>72</v>
       </c>
-    </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL224">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>260</v>
       </c>
@@ -21535,8 +22460,12 @@
       <c r="AF225" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL225">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>261</v>
       </c>
@@ -21621,8 +22550,12 @@
       <c r="AF226" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL226">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>262</v>
       </c>
@@ -21707,8 +22640,12 @@
       <c r="AF227" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL227">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>263</v>
       </c>
@@ -21793,8 +22730,12 @@
       <c r="AF228" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL228">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>264</v>
       </c>
@@ -21873,8 +22814,12 @@
       <c r="AB229">
         <v>80</v>
       </c>
-    </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL229">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>265</v>
       </c>
@@ -21950,8 +22895,12 @@
       <c r="AF230" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="231" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL230">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>266</v>
       </c>
@@ -22030,8 +22979,12 @@
       <c r="AE231">
         <v>200</v>
       </c>
-    </row>
-    <row r="232" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL231">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>267</v>
       </c>
@@ -22113,8 +23066,12 @@
       <c r="AE232">
         <v>40</v>
       </c>
-    </row>
-    <row r="233" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL232">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>268</v>
       </c>
@@ -22199,8 +23156,12 @@
       <c r="AH233">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL233">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>269</v>
       </c>
@@ -22282,8 +23243,12 @@
       <c r="AF234" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL234">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>270</v>
       </c>
@@ -22368,8 +23333,12 @@
       <c r="AF235" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL235">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>271</v>
       </c>
@@ -22448,8 +23417,12 @@
       <c r="AF236" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="237" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL236">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>272</v>
       </c>
@@ -22531,8 +23504,12 @@
       <c r="AE237">
         <v>300</v>
       </c>
-    </row>
-    <row r="238" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL237">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>273</v>
       </c>
@@ -22611,8 +23588,12 @@
       <c r="AB238">
         <v>100</v>
       </c>
-    </row>
-    <row r="239" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL238">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>274</v>
       </c>
@@ -22697,8 +23678,12 @@
       <c r="AF239" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL239">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>275</v>
       </c>
@@ -22783,8 +23768,12 @@
       <c r="AE240">
         <v>26</v>
       </c>
-    </row>
-    <row r="241" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL240">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>276</v>
       </c>
@@ -22866,8 +23855,12 @@
       <c r="AE241">
         <v>55</v>
       </c>
-    </row>
-    <row r="242" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL241">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>277</v>
       </c>
@@ -22952,8 +23945,12 @@
       <c r="AE242">
         <v>42</v>
       </c>
-    </row>
-    <row r="243" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL242">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>278</v>
       </c>
@@ -23038,8 +24035,12 @@
       <c r="AE243">
         <v>164</v>
       </c>
-    </row>
-    <row r="244" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL243">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>279</v>
       </c>
@@ -23124,8 +24125,12 @@
       <c r="AF244" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="245" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL244">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>280</v>
       </c>
@@ -23201,8 +24206,12 @@
       <c r="AJ245" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="246" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL245">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>281</v>
       </c>
@@ -23287,8 +24296,12 @@
       <c r="AF246" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="247" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL246">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>282</v>
       </c>
@@ -23370,8 +24383,12 @@
       <c r="AF247" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="248" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL247">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>283</v>
       </c>
@@ -23456,8 +24473,12 @@
       <c r="AE248">
         <v>100</v>
       </c>
-    </row>
-    <row r="249" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL248">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>284</v>
       </c>
@@ -23539,8 +24560,12 @@
       <c r="AF249" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="250" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL249">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>285</v>
       </c>
@@ -23622,8 +24647,12 @@
       <c r="AE250">
         <v>100</v>
       </c>
-    </row>
-    <row r="251" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL250">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>286</v>
       </c>
@@ -23708,8 +24737,12 @@
       <c r="AF251" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="252" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL251">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>287</v>
       </c>
@@ -23794,8 +24827,12 @@
       <c r="AE252">
         <v>120</v>
       </c>
-    </row>
-    <row r="253" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL252">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>288</v>
       </c>
@@ -23880,8 +24917,12 @@
       <c r="AE253">
         <v>15</v>
       </c>
-    </row>
-    <row r="254" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL253">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>289</v>
       </c>
@@ -23966,8 +25007,12 @@
       <c r="AF254" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="255" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL254">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>290</v>
       </c>
@@ -24052,8 +25097,12 @@
       <c r="AE255">
         <v>45</v>
       </c>
-    </row>
-    <row r="256" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL255">
+        <f t="shared" ca="1" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>291</v>
       </c>
@@ -24138,8 +25187,12 @@
       <c r="AF256" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="257" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL256">
+        <f t="shared" ca="1" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>292</v>
       </c>
@@ -24224,8 +25277,12 @@
       <c r="AF257" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="258" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL257">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>293</v>
       </c>
@@ -24310,8 +25367,12 @@
       <c r="AF258" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="259" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL258">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>294</v>
       </c>
@@ -24393,8 +25454,12 @@
       <c r="AB259">
         <v>81</v>
       </c>
-    </row>
-    <row r="260" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL259">
+        <f t="shared" ref="AL259:AL322" ca="1" si="4">RANDBETWEEN(1,7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>295</v>
       </c>
@@ -24476,8 +25541,12 @@
       <c r="AF260" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="261" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL260">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>296</v>
       </c>
@@ -24553,8 +25622,12 @@
       <c r="AF261" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="262" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL261">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>297</v>
       </c>
@@ -24633,8 +25706,12 @@
       <c r="AB262">
         <v>140</v>
       </c>
-    </row>
-    <row r="263" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL262">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>298</v>
       </c>
@@ -24713,8 +25790,12 @@
       <c r="AB263">
         <v>120</v>
       </c>
-    </row>
-    <row r="264" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL263">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>299</v>
       </c>
@@ -24796,8 +25877,12 @@
       <c r="AB264">
         <v>148</v>
       </c>
-    </row>
-    <row r="265" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL264">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>300</v>
       </c>
@@ -24882,8 +25967,12 @@
       <c r="AF265" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="266" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL265">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>301</v>
       </c>
@@ -24959,8 +26048,12 @@
       <c r="AA266" s="2" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="267" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL266">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>302</v>
       </c>
@@ -25039,8 +26132,12 @@
       <c r="AB267">
         <v>109</v>
       </c>
-    </row>
-    <row r="268" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL267">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>303</v>
       </c>
@@ -25122,8 +26219,12 @@
       <c r="AD268" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="269" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL268">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>304</v>
       </c>
@@ -25205,8 +26306,12 @@
       <c r="AE269">
         <v>300</v>
       </c>
-    </row>
-    <row r="270" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL269">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>305</v>
       </c>
@@ -25294,8 +26399,12 @@
       <c r="AH270">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="271" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL270">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>306</v>
       </c>
@@ -25377,8 +26486,12 @@
       <c r="AE271">
         <v>2</v>
       </c>
-    </row>
-    <row r="272" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AL271">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>307</v>
       </c>
@@ -25457,8 +26570,12 @@
       <c r="AB272">
         <v>148</v>
       </c>
-    </row>
-    <row r="273" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL272">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>308</v>
       </c>
@@ -25540,8 +26657,12 @@
       <c r="AF273" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="274" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL273">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>309</v>
       </c>
@@ -25632,8 +26753,12 @@
       <c r="AI274">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="275" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL274">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>310</v>
       </c>
@@ -25721,8 +26846,12 @@
       <c r="AG275">
         <v>18.600000000000001</v>
       </c>
-    </row>
-    <row r="276" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL275">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>311</v>
       </c>
@@ -25804,8 +26933,12 @@
       <c r="AF276" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="277" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL276">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>312</v>
       </c>
@@ -25887,8 +27020,12 @@
       <c r="AB277">
         <v>125</v>
       </c>
-    </row>
-    <row r="278" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL277">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>313</v>
       </c>
@@ -25970,8 +27107,12 @@
       <c r="AB278">
         <v>160</v>
       </c>
-    </row>
-    <row r="279" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL278">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>314</v>
       </c>
@@ -26053,8 +27194,12 @@
       <c r="AA279" s="2" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="280" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL279">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>315</v>
       </c>
@@ -26133,8 +27278,12 @@
       <c r="AF280" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="281" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL280">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>316</v>
       </c>
@@ -26219,8 +27368,12 @@
       <c r="AH281">
         <v>9.3000000000000007</v>
       </c>
-    </row>
-    <row r="282" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL281">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>317</v>
       </c>
@@ -26302,8 +27455,12 @@
       <c r="AD282" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="283" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL282">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>318</v>
       </c>
@@ -26385,8 +27542,12 @@
       <c r="AD283" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="284" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL283">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>319</v>
       </c>
@@ -26465,8 +27626,12 @@
       <c r="AA284" s="2" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="285" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL284">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>320</v>
       </c>
@@ -26548,8 +27713,12 @@
       <c r="AB285">
         <v>135</v>
       </c>
-    </row>
-    <row r="286" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL285">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>321</v>
       </c>
@@ -26628,8 +27797,12 @@
       <c r="AD286" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="287" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL286">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>322</v>
       </c>
@@ -26711,8 +27884,12 @@
       <c r="AD287" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="288" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL287">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>323</v>
       </c>
@@ -26794,8 +27971,12 @@
       <c r="AB288">
         <v>156</v>
       </c>
-    </row>
-    <row r="289" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL288">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>324</v>
       </c>
@@ -26874,8 +28055,12 @@
       <c r="AF289" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="290" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL289">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>325</v>
       </c>
@@ -26957,8 +28142,12 @@
       <c r="AF290" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="291" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL290">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>326</v>
       </c>
@@ -27043,8 +28232,12 @@
       <c r="AF291" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="292" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL291">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>327</v>
       </c>
@@ -27123,8 +28316,12 @@
       <c r="AF292" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="293" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL292">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>328</v>
       </c>
@@ -27209,8 +28406,12 @@
       <c r="AF293" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="294" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL293">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>329</v>
       </c>
@@ -27292,8 +28493,12 @@
       <c r="AE294">
         <v>250</v>
       </c>
-    </row>
-    <row r="295" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL294">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>330</v>
       </c>
@@ -27372,8 +28577,12 @@
       <c r="AE295">
         <v>121</v>
       </c>
-    </row>
-    <row r="296" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL295">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>331</v>
       </c>
@@ -27452,8 +28661,12 @@
       <c r="AB296">
         <v>110</v>
       </c>
-    </row>
-    <row r="297" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL296">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>141</v>
       </c>
@@ -27532,8 +28745,12 @@
       <c r="AF297" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="298" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL297">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>332</v>
       </c>
@@ -27615,8 +28832,12 @@
       <c r="AE298">
         <v>500</v>
       </c>
-    </row>
-    <row r="299" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL298">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>333</v>
       </c>
@@ -27692,8 +28913,12 @@
       <c r="AF299" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="300" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL299">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>334</v>
       </c>
@@ -27775,8 +29000,12 @@
       <c r="AE300">
         <v>45</v>
       </c>
-    </row>
-    <row r="301" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL300">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>335</v>
       </c>
@@ -27858,8 +29087,12 @@
       <c r="AE301">
         <v>450</v>
       </c>
-    </row>
-    <row r="302" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL301">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>336</v>
       </c>
@@ -27944,8 +29177,12 @@
       <c r="AF302" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="303" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL302">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>337</v>
       </c>
@@ -28036,8 +29273,12 @@
       <c r="AI303">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="304" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AL303">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>338</v>
       </c>
@@ -28119,8 +29360,12 @@
       <c r="AF304" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="305" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL304">
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>339</v>
       </c>
@@ -28205,8 +29450,12 @@
       <c r="AF305" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="306" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL305">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>340</v>
       </c>
@@ -28291,8 +29540,12 @@
       <c r="AF306" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="307" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL306">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>341</v>
       </c>
@@ -28377,8 +29630,12 @@
       <c r="AF307" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="308" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL307">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>342</v>
       </c>
@@ -28463,8 +29720,12 @@
       <c r="AF308" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="309" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL308">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>343</v>
       </c>
@@ -28552,8 +29813,12 @@
       <c r="AG309">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="310" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL309">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>344</v>
       </c>
@@ -28635,8 +29900,12 @@
       <c r="AF310" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="311" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL310">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>345</v>
       </c>
@@ -28721,8 +29990,12 @@
       <c r="AF311" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="312" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL311">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>346</v>
       </c>
@@ -28804,8 +30077,12 @@
       <c r="AF312" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="313" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL312">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>347</v>
       </c>
@@ -28890,8 +30167,12 @@
       <c r="AF313" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="314" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL313">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>348</v>
       </c>
@@ -28976,8 +30257,12 @@
       <c r="AF314" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="315" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL314">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>349</v>
       </c>
@@ -29062,8 +30347,12 @@
       <c r="AF315" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="316" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL315">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>350</v>
       </c>
@@ -29145,8 +30434,12 @@
       <c r="AK316" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="317" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL316">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>351</v>
       </c>
@@ -29231,8 +30524,12 @@
       <c r="AF317" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="318" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL317">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>352</v>
       </c>
@@ -29317,8 +30614,12 @@
       <c r="AF318" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="319" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL318">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>353</v>
       </c>
@@ -29403,8 +30704,12 @@
       <c r="AE319">
         <v>37</v>
       </c>
-    </row>
-    <row r="320" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="AL319">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="320" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>354</v>
       </c>
@@ -29489,8 +30794,12 @@
       <c r="AE320">
         <v>86</v>
       </c>
-    </row>
-    <row r="321" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL320">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="321" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>355</v>
       </c>
@@ -29575,8 +30884,12 @@
       <c r="AE321">
         <v>32</v>
       </c>
-    </row>
-    <row r="322" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL321">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>356</v>
       </c>
@@ -29658,8 +30971,12 @@
       <c r="AF322" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="323" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL322">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>357</v>
       </c>
@@ -29744,8 +31061,12 @@
       <c r="AF323" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="324" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL323">
+        <f t="shared" ref="AL323:AL331" ca="1" si="5">RANDBETWEEN(1,7)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="324" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>358</v>
       </c>
@@ -29824,8 +31145,12 @@
       <c r="AB324">
         <v>152</v>
       </c>
-    </row>
-    <row r="325" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL324">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>359</v>
       </c>
@@ -29907,8 +31232,12 @@
       <c r="AF325" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="326" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL325">
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>360</v>
       </c>
@@ -29990,8 +31319,12 @@
       <c r="AD326" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="327" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL326">
+        <f t="shared" ca="1" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>361</v>
       </c>
@@ -30070,8 +31403,12 @@
       <c r="AJ327" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="328" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL327">
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>362</v>
       </c>
@@ -30153,8 +31490,12 @@
       <c r="AB328">
         <v>77</v>
       </c>
-    </row>
-    <row r="329" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL328">
+        <f t="shared" ca="1" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="329" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>363</v>
       </c>
@@ -30239,8 +31580,12 @@
       <c r="AF329" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="330" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL329">
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>364</v>
       </c>
@@ -30322,8 +31667,12 @@
       <c r="AA330" s="2" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="331" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AL330">
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>365</v>
       </c>
@@ -30395,6 +31744,10 @@
       </c>
       <c r="AF331" t="s">
         <v>739</v>
+      </c>
+      <c r="AL331">
+        <f t="shared" ca="1" si="5"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/OnTheSnow_v1.xlsx
+++ b/OnTheSnow_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoursesUSU\Final_Semester\Intro_Reg_ML\DATA5600\data-5600\Project1\Data-5600-Project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B3EBDB-9E3B-404B-AFF1-9B612BFA7789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09EBAD5-7CB3-428B-9D09-C6EF1461D897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24687,7 +24687,9 @@
         <v>177</v>
       </c>
       <c r="AL245" s="5"/>
-      <c r="AM245" s="5"/>
+      <c r="AM245" s="5">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="246" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
@@ -25959,7 +25961,9 @@
         <v>81</v>
       </c>
       <c r="AL259" s="5"/>
-      <c r="AM259" s="5"/>
+      <c r="AM259" s="5">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="260" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
